--- a/public/datos/4.2_Matriz_riesgos.xlsx
+++ b/public/datos/4.2_Matriz_riesgos.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Riesgos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Escala" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Escala_Severidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Matriz_Riesgos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,460 +427,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Proceso</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Probabilidad (1-5)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Impacto (1-5)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Nivel de riesgo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Nivel</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>Código de Actividad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uso de documentos obsoletos en producción</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Listado maestro y retiro de copias obsoletas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Andrés Brito</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>Título del Caso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Incumplimiento de requisitos legales ambientales</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Gestión ambiental</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Matriz legal con seguimiento trimestral</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Laura Pimienta</t>
+          <t>Matriz cuantitativa de evaluación y control de riesgos SIG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>Organización</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accidente por trabajo en alturas</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Seguridad y salud en el trabajo</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Permisos de trabajo y uso de EPP certificado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Daniela Epiayú</t>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>1. Situación Problema</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pérdida de clientes por PQRS sin respuesta</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Comercial y ventas</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Seguimiento semanal de PQRS abiertas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Marelvis Ospino</t>
+          <t>Lácteos del Caribe enfrenta riesgos operativos y de SST: amoníaco en cavas, contaminación en pasteurización, alturas y sanciones ambientales.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>2. Misión del Aprendiz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Materia prima no conforme del proveedor</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Compras</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Evaluación y reevaluación de proveedores</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Camilo Iguarán</t>
+          <t>Construir la matriz cuantitativa de riesgos con cálculo de severidad (P×I), clasificación por escala de severidad, semaforización de 4 colores y control obligatorio.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>Requerimiento 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Falla de equipos por falta de mantenimiento</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Plan de mantenimiento preventivo</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Andrés Brito</t>
+          <t>Validación de Escalas: Restringir Probabilidad e Impacto a números enteros del 1 al 5.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>Requerimiento 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rotación de personal clave</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Talento humano</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Plan de sucesión y entrenamiento cruzado</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Yesenia Uriana</t>
+          <t>Severidad Inherente: Formular Nivel de Riesgo = Probabilidad * Impacto (1 a 25).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>Requerimiento 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retrasos en entregas por fallas logísticas</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Logística y distribución</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Rutas alternas y vehículo de respaldo</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Kevin Fragozo</t>
+          <t>Clasificación Automática: Clasificar con SI anidado o BUSCARV aproximado apoyado en Escala_Severidad: 1-4 Bajo, 5-9 Medio, 10-16 Alto, 17-25 Extremo.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>Requerimiento 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pérdida de información del SIG</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Gestión de la calidad</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Copias de seguridad semanales en la nube</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Laura Pimienta</t>
+          <t>Semaforización 4 Colores: Verde (Bajo), Amarillo (Medio), Naranja (Alto) y Rojo (Extremo).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>Requerimiento 5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Contaminación cruzada del producto</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Instructivo de limpieza y desinfección</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Andrés Brito</t>
+          <t>Acción Inmediata: Si el riesgo es Alto o Extremo -&gt; 'CONTROL PRIORITARIO REQUERIDO'; de lo contrario -&gt; 'Monitoreo Periódico'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>Dificultad Clave / Regla Técnica</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hallazgos de auditoría sin cierre</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Gestión de la calidad</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Plan de acción con fechas y responsables</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Laura Pimienta</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R-12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Derrame de químicos de limpieza</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Seguridad y salud en el trabajo</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kit antiderrames y capacitación</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Daniela Epiayú</t>
+          <t>Configura las 4 reglas condicionales ordenadamente para que los riesgos extremos (rojos) no queden ocultos por rangos menores.</t>
         </is>
       </c>
     </row>
@@ -894,34 +589,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desde</t>
+          <t>Rango Mínimo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Hasta</t>
+          <t>Rango Máximo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Nivel</t>
+          <t>Nivel Cualitativo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Color Asociado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Acción de Control</t>
         </is>
       </c>
     </row>
@@ -942,6 +643,11 @@
           <t>Verde</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Monitoreo periódico</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -960,6 +666,11 @@
           <t>Amarillo</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Procedimiento estándar y seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +689,11 @@
           <t>Naranja</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Control preventivo inmediato y responsable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -994,6 +710,485 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Rojo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Control prioritario urgente y plan de contingencia</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descripción del Riesgo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Probabilidad (1-5)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Impacto (1-5)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Nivel de Riesgo (=P*I)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Clasificación Severidad</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Control</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Acción Inmediata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Uso de documentos obsoletos en producción</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Listado maestro y retiro de copias obsoletas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Andrés Brito</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Incumplimiento de requisitos legales ambientales</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gestión ambiental</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Matriz legal con seguimiento trimestral</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Laura Pimienta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Accidente por trabajo en alturas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seguridad y salud en el trabajo</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Permisos de trabajo y uso de EPP certificado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Daniela Epiayú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pérdida de clientes por PQRS sin respuesta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comercial y ventas</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Seguimiento semanal de PQRS abiertas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Marelvis Ospino</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Materia prima no conforme del proveedor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Compras</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Evaluación y reevaluación de proveedores</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Camilo Iguarán</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Falla de equipos por falta de mantenimiento</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Plan de mantenimiento preventivo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Andrés Brito</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rotación de personal clave</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Talento humano</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Plan de sucesión y entrenamiento cruzado</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yesenia Uriana</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Retrasos en entregas por fallas logísticas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Logística y distribución</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Rutas alternas y vehículo de respaldo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Kevin Fragozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pérdida de información del SIG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Copias de seguridad semanales en la nube</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Laura Pimienta</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Contaminación cruzada del producto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Instructivo de limpieza y desinfección</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Andrés Brito</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hallazgos de auditoría sin cierre</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Plan de acción con fechas y responsables</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Laura Pimienta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Derrame de químicos de limpieza</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seguridad y salud en el trabajo</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kit antiderrames y capacitación</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Daniela Epiayú</t>
         </is>
       </c>
     </row>
